--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260625.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260625.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>493,581,352</t>
+          <t>234,848,170</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>234,848,170</t>
+          <t>493,581,352</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>335,082,015</t>
+          <t>1,996,993</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,996,993</t>
+          <t>64,234,490</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>64,234,490</t>
+          <t>335,082,015</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>7,312,086</t>
+          <t>41,605,984</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>41,605,984</t>
+          <t>7,312,086</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>105,113,284</t>
+          <t>238,254,299</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>238,254,299</t>
+          <t>105,113,284</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>3,803,091</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>3,803,091</t>
+          <t>778</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
